--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/02. Trả bảo hành/TBH_SEA_051026.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/02. Trả bảo hành/TBH_SEA_051026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 10\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB71888-93BE-428A-A7EC-CCE7636720AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234F8067-CB41-4BBD-943A-EAEA5F44B2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,9 +92,6 @@
     <t>TPB. Bảo Hành</t>
   </si>
   <si>
-    <t>Khách hàng/ người đại diện: Đại lý SEA</t>
-  </si>
-  <si>
     <t>005581051083500</t>
   </si>
   <si>
@@ -144,6 +141,9 @@
   </si>
   <si>
     <t>Hà Nội, ngày 05 tháng 10 năm 2026</t>
+  </si>
+  <si>
+    <t>Khách hàng/ người đại diện: Đại lý SEA.</t>
   </si>
 </sst>
 </file>
@@ -522,6 +522,42 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="13"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -555,44 +591,8 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1090,73 +1090,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="39" t="s">
+      <c r="A1" s="50"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="42"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="54"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="43" t="s">
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="45"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="46" t="s">
+      <c r="A4" s="50"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="48"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1166,7 +1166,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1215,7 +1215,7 @@
       <c r="B10" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="38" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="12" t="s">
@@ -1243,192 +1243,192 @@
         <v>1</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="60" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>22</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="21"/>
+      <c r="G11" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="61" t="s">
-        <v>33</v>
-      </c>
       <c r="H11" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I11" s="21"/>
-      <c r="J11" s="58"/>
+      <c r="J11" s="40"/>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>2</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="60" t="s">
-        <v>24</v>
+        <v>30</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>23</v>
       </c>
       <c r="D12" s="21"/>
       <c r="E12" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="21"/>
+      <c r="G12" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="61" t="s">
-        <v>33</v>
-      </c>
       <c r="H12" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I12" s="21"/>
-      <c r="J12" s="58"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20">
         <v>3</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="60" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>24</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="21"/>
+      <c r="G13" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="61" t="s">
-        <v>33</v>
-      </c>
       <c r="H13" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I13" s="21"/>
-      <c r="J13" s="58"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <v>4</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="60" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>25</v>
       </c>
       <c r="D14" s="21"/>
       <c r="E14" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" s="21"/>
-      <c r="G14" s="61" t="s">
-        <v>34</v>
+      <c r="G14" s="43" t="s">
+        <v>33</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I14" s="21"/>
-      <c r="J14" s="58"/>
+      <c r="J14" s="40"/>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>5</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="60" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>26</v>
       </c>
       <c r="D15" s="21"/>
       <c r="E15" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15" s="21"/>
-      <c r="G15" s="61" t="s">
-        <v>35</v>
+      <c r="G15" s="43" t="s">
+        <v>34</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I15" s="21"/>
-      <c r="J15" s="58"/>
+      <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>6</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>27</v>
       </c>
       <c r="D16" s="21"/>
       <c r="E16" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" s="21"/>
-      <c r="G16" s="61" t="s">
-        <v>35</v>
+      <c r="G16" s="43" t="s">
+        <v>34</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I16" s="21"/>
-      <c r="J16" s="58"/>
+      <c r="J16" s="40"/>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="20">
         <v>7</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="60" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>28</v>
       </c>
       <c r="D17" s="21"/>
       <c r="E17" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" s="21"/>
-      <c r="G17" s="61" t="s">
-        <v>34</v>
+      <c r="G17" s="43" t="s">
+        <v>33</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I17" s="21"/>
-      <c r="J17" s="58"/>
+      <c r="J17" s="40"/>
     </row>
     <row r="18" spans="1:10" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
         <v>8</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="57" t="s">
         <v>30</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>29</v>
       </c>
       <c r="D18" s="21"/>
       <c r="E18" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="21"/>
+      <c r="G18" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="21"/>
-      <c r="G18" s="61" t="s">
-        <v>33</v>
-      </c>
       <c r="H18" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I18" s="21"/>
-      <c r="J18" s="59"/>
+      <c r="J18" s="41"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="31"/>
@@ -1442,34 +1442,34 @@
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="52" t="s">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="53" t="s">
+      <c r="A21" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53" t="s">
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26"/>
@@ -1516,19 +1516,19 @@
       <c r="I25" s="16"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="54" t="s">
+      <c r="A26" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
@@ -1542,12 +1542,17 @@
       <c r="I27" s="7"/>
     </row>
     <row r="29" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="46"/>
     </row>
     <row r="68" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="F20:I20"/>
@@ -1556,14 +1561,9 @@
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="21" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -1577,33 +1577,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="52" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
       <c r="I1" s="25"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
       <c r="I2" s="15"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1651,18 +1651,18 @@
       <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54" t="s">
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
       <c r="I7" s="14"/>
     </row>
   </sheetData>
